--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0142.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0142.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rover lại cứu nguy một lần nữa!</t>
+          <t>Vận Mệnh Giả lại cứu nguy một lần nữa!</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ừ. Chính ta đây.</t>
+          <t>Ừ. Chính tao đây.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Đợi đến khi ta cho ngươi xem màn trình diễn đèn lồng hoành tráng nhất Hội Chợ! Ta biết chỗ ngồi xem đẹp nhất đấy!</t>
+          <t>Đợi đến khi tao cho mày xem màn trình diễn đèn lồng hoành tráng nhất Hội Chợ! Tao biết chỗ ngồi xem đẹp nhất đấy!</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Của ta là tổ chức Hội chợ Trăng Sáng để thu hút đám đông và cho mọi người có một khoảng thời gian tuyệt vời.</t>
+          <t>Của tao là tổ chức Hội chợ Trăng Sáng để thu hút đám đông và cho mọi người có một khoảng thời gian tuyệt vời.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Vậy thì thỏa thuận thế nhé! Nhớ lời ta đấy, có bọn ta ở đây, cậu sẽ được trải nghiệm một Lễ Hội Đuổi Trăng khó quên suốt đời!</t>
+          <t>Vậy thì thỏa thuận thế nhé! Nhớ lời tao đấy, có bọn tao ở đây, cậu sẽ được trải nghiệm một Lễ Hội Đuổi Trăng khó quên suốt đời!</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Ta hiểu rồi.</t>
+          <t>Tao hiểu rồi.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Chỉ là biện pháp tạm thời thôi. Sau này ta sẽ kiểm tra kỹ càng hơn.</t>
+          <t>Chỉ là biện pháp tạm thời thôi. Sau này tao sẽ kiểm tra kỹ càng hơn.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Anh biết tôi à?</t>
+          <t>Cậu biết tớ à?</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Cảm ơn cậu đã đến, Rover.</t>
+          <t>Cảm ơn cậu đã đến, Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Anh ấy đã chết vì Waveworn... Tôi nghĩ... nếu Quả Cầu Sonoro này có liên quan đến anh ấy, chắc hẳn nó chứa đựng những lời nhắn của anh ấy dành cho tôi.</t>
+          <t>Anh ấy đã chết vì Waveworn... Tôi nghĩ... nếu Sonoro Sphere này có liên quan đến anh ấy, chắc hẳn nó chứa đựng những lời nhắn của anh ấy dành cho tôi.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Ta đã hứa với bạn bè là tối nay sẽ cùng nhau vui chơi ở Hội chợ Trăng Sáng. Không thể để vụ này phá hỏng không khí lễ hội.</t>
+          <t>Tao đã hứa với bạn bè là tối nay sẽ cùng nhau vui chơi ở Hội chợ Trăng Sáng. Không thể để vụ này phá hỏng không khí lễ hội.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro à? Đối với ta thì chỉ là sân chơi thôi.</t>
+          <t>Sonoro Sphere à? Đối với tao thì chỉ là sân chơi thôi.</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Sếp ơi, nhìn kìa! {Male=Anh ấy;Female=Cô ấy} quay lại rồi!</t>
+          <t>Sếp ơi, nhìn kìa! {Male=He;Female=She} quay lại rồi!</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>{PlayerName}, Rover báo cáo có mặt!</t>
+          <t>{PlayerName}, Vận Mệnh Giả báo cáo có mặt!</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Ta còn không thể vào được bên trong, nói gì đến tìm thứ mình cần...</t>
+          <t>Tao còn không thể vào được bên trong, nói gì đến tìm thứ mình cần...</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Dù ta giấu ở đâu, ngươi vẫn tìm ra được hết. Chết tiệt, ngươi còn biết phòng ta rõ hơn cả ta luôn.</t>
+          <t>Dù tao giấu ở đâu, mày vẫn tìm ra được hết. Chết tiệt, mày còn biết phòng tao rõ hơn cả tao luôn.</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Cậu cứ chọn bất kỳ bức tranh nào của tôi để làm lời xin lỗi nhé? Tôi nhất định muốn cậu chọn một bức...</t>
+          <t>bạn cứ chọn bất kỳ bức tranh nào của tôi để làm lời xin lỗi nhé? Tôi nhất định muốn bạn chọn một bức...</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Tớ phát hiện vài tần số lạ trong người nó. Không biết có phải do ảnh hưởng của Quả Cầu Sonoro không.</t>
+          <t>Tớ phát hiện vài tần số lạ trong người nó. Không biết có phải do ảnh hưởng của Sonoro Sphere không.</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ cậu sẽ lao ngay vào nghiên cứu nguyên nhân cơ.</t>
+          <t>Tao cứ nghĩ cậu sẽ lao ngay vào nghiên cứu nguyên nhân cơ.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Thường thì ta sẽ làm thế. Nhưng lần này thì không, vì ta đã hứa tặng ngươi một món quà rồi.</t>
+          <t>Thường thì tao sẽ làm thế. Nhưng lần này thì không, vì tao đã hứa tặng mày một món quà rồi.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Chưa. Vậy nên ta mới chuẩn bị viết một cái.</t>
+          <t>Chưa. Vậy nên tao mới chuẩn bị viết một cái.</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>{Male=Nghe nói vài người bán hàng giảm giá cho những ai đi cùng nhau à?;Female=Nghe nói Lễ Hội Đuổi Trăng là dịp để sum vầy phải không?}</t>
+          <t>{Male=They say some vendors offer discounts to people visiting together?;Female=They say the Moon-Chasing Festival is a time for reunions?}</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>{Male=Ừ... Một vài nơi thôi.;Female=Theo truyền thống thì đúng vậy...}</t>
+          <t>{Male=Yes... Some of them.;Female=Traditionally, yes…}</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>{Male=Đi cùng anh nhé. Coi như thêm một đặc quyền khi làm việc cho Moontree Lodge.;Female=Đi cùng chị nhé. Không phải là sum họp nếu còn lại mình em cô đơn.}</t>
+          <t>{Male=Come with me, then. Make it another perk of working for the Moontree Lodge.;Female=Come with me, then. It's not a reunion when you're left alone.}</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>R-really? Bạn aren't angry at us? Cảm ơn, you're so nice...:::Thật à? Cậu không giận chúng tớ à? Cảm ơn cậu, cậu tốt quá...</t>
+          <t>R-really? You aren't angry at us? Thank you, you're so nice...:::Thật à? Cậu không giận chúng tớ à? Cảm ơn cậu, cậu tốt quá...</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Tất nhiên là được chứ! Chúng ta còn có thể phong ngươi làm ông chủ mới nữa cơ!</t>
+          <t>Tất nhiên là được chứ! Chúng tao còn có thể phong mày làm ông chủ mới nữa cơ!</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Ta không thích ở một mình. Không biết cậu có thấy thế không.</t>
+          <t>Tao không thích ở một mình. Không biết cậu có thấy thế không.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Okay..</t>
+          <t>Ừm...</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Thực ra ta chỉ nói vậy vì ta coi ngươi là người bạn và đối thủ duy nhất của ta.</t>
+          <t>Thực ra tao chỉ nói vậy vì tao coi mày là người bạn và đối thủ duy nhất của tao.</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Mấy lần Hội Săn Trăng, cậu chẳng bao giờ về nhà... Đang bận giúp người khác à?</t>
+          <t>Mấy lần Hội Săn Trăng, mày chẳng bao giờ về nhà... Đang bận giúp người khác à?</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Ma ám à? Hừ! Không đời nào. Thừa nhận đi, ta chỉ đang sống miễn phí trong đầu ngươi thôi.</t>
+          <t>Ma ám à? Hừ! Không đời nào. Thừa nhận đi, tao chỉ đang sống miễn phí trong đầu mày thôi.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Ta không thể tiếp tục nữa... Mọi thứ kết thúc rồi... Ta vô dụng thật...</t>
+          <t>Tao không thể tiếp tục nữa... Mọi thứ kết thúc rồi... Tao vô dụng thật...</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Không phải lỗi tại ta... Mà là tại bọn chúng! Không, tại cả thế giới này! Cả thế giới này đều sai hết rồi! Hahahaha!</t>
+          <t>Không phải lỗi tại tao... Mà là tại bọn chúng! Không, tại cả thế giới này! Cả thế giới này đều sai hết rồi! Hahahaha!</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Mệt quá… Ta muốn biến mất luôn… Đồ quái quỷ gì chứ!</t>
+          <t>Mệt quá… Tao muốn biến mất luôn… Đồ quái quỷ gì chứ!</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Được! Ta sẽ tự làm!</t>
+          <t>Được! Tao sẽ tự làm!</t>
         </is>
       </c>
     </row>
